--- a/Daily_Adjustments_Template.xlsx
+++ b/Daily_Adjustments_Template.xlsx
@@ -399,50 +399,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:D5"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="24.83203125" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="45.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="38.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>วันที่ (DD/MM/YYYY)</v>
+        <v>วันที่</v>
       </c>
       <c r="B1" t="str">
         <v>รหัสพนักงาน</v>
       </c>
       <c r="C1" t="str">
-        <v>ชื่อ - นามสกุล</v>
+        <v>เครื่องจักรที่ไปทำ OT (OT Machine)</v>
       </c>
       <c r="D1" t="str">
-        <v>แผนก/Cost Center</v>
-      </c>
-      <c r="E1" t="str">
-        <v>เครื่องประจำเดิม</v>
-      </c>
-      <c r="F1" t="str">
-        <v>1. ย้ายเครื่องกะปกติ</v>
-      </c>
-      <c r="G1" t="str">
-        <v>2. ย้ายเครื่องทำ OT</v>
-      </c>
-      <c r="H1" t="str">
-        <v>3. เวลาเข้าพิเศษ (HH:MM)</v>
-      </c>
-      <c r="I1" t="str">
-        <v>4. เวลาออกพิเศษ (HH:MM)</v>
-      </c>
-      <c r="J1" t="str">
-        <v>เหตุผล / หมายเหตุ</v>
+        <v>เวลา</v>
       </c>
     </row>
     <row r="2">
@@ -453,28 +429,10 @@
         <v>11848</v>
       </c>
       <c r="C2" t="str">
-        <v>วีระพันธ์ นุตะดี</v>
+        <v>320 BANBURY # 2</v>
       </c>
       <c r="D2" t="str">
-        <v>3200</v>
-      </c>
-      <c r="E2" t="str">
-        <v>320 BANBURY # 1</v>
-      </c>
-      <c r="F2" t="str">
         <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>320 BANBURY # 2</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
-        <v>ทำ OT กะ 3 ช่วย Mixer 2</v>
       </c>
     </row>
     <row r="3">
@@ -482,31 +440,13 @@
         <v>13/09/2026</v>
       </c>
       <c r="B3" t="str">
-        <v>12128</v>
+        <v>03027</v>
       </c>
       <c r="C3" t="str">
-        <v>พายุ บุญมาใส</v>
+        <v>320 BANBURY # 2</v>
       </c>
       <c r="D3" t="str">
-        <v>3200</v>
-      </c>
-      <c r="E3" t="str">
-        <v>320 BANBURY # 1</v>
-      </c>
-      <c r="F3" t="str">
-        <v>320 BANBURY # 2</v>
-      </c>
-      <c r="G3" t="str">
         <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v>ย้ายไปประจำ Mixer 2 กะ 1 แทนคนที่ลา</v>
       </c>
     </row>
     <row r="4">
@@ -517,28 +457,10 @@
         <v>12140</v>
       </c>
       <c r="C4" t="str">
-        <v>ถวิล ลืมอินทร์</v>
+        <v/>
       </c>
       <c r="D4" t="str">
-        <v>3200</v>
-      </c>
-      <c r="E4" t="str">
-        <v>320 BANBURY # 1</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v>11:00</v>
-      </c>
-      <c r="I4" t="str">
-        <v>19:00</v>
-      </c>
-      <c r="J4" t="str">
-        <v>หัวหน้างานสั่งให้มาทำงานเวลาพิเศษ 11:00-19:00 (ไม่คิดสาย)</v>
+        <v>11:00 - 19:00</v>
       </c>
     </row>
     <row r="5">
@@ -546,36 +468,18 @@
         <v>13/09/2026</v>
       </c>
       <c r="B5" t="str">
-        <v>12412</v>
+        <v>12128</v>
       </c>
       <c r="C5" t="str">
-        <v>พิษณุ ช้างชน</v>
+        <v>320 BANBURY # 2</v>
       </c>
       <c r="D5" t="str">
-        <v>4300</v>
-      </c>
-      <c r="E5" t="str">
-        <v>430 Quad</v>
-      </c>
-      <c r="F5" t="str">
         <v/>
-      </c>
-      <c r="G5" t="str">
-        <v>430 6"x8" Tuber</v>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v>ทำ OT กะ 3 ไปช่วยเครื่อง Tuber 6x8</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -837,7 +741,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>หัวข้อ</v>
+        <v>คอลัมน์ (4 ช่อง)</v>
       </c>
       <c r="B1" t="str">
         <v>คำอธิบาย</v>
@@ -845,34 +749,34 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>รูปแบบที่ 1: กะตัวเอง ย้ายไปทำเครื่องอื่น (Normal Shift Transfer)</v>
+        <v>1. วันที่</v>
       </c>
       <c r="B2" t="str">
-        <v>กรอกชื่อเครื่องจักรเป้าหมายในช่อง "1. ย้ายเครื่องกะปกติ" -&gt; ระบบจะโอนยอดคนปกติ 1 คนไปนับที่เครื่องใหม่ทันที</v>
+        <v>วันที่ที่ต้องการปรับเปลี่ยน เช่น 13/09/2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>รูปแบบที่ 2: กะตัวเองทำเครื่องเดิม และทำ OT เครื่องอื่น (OT Transfer)</v>
+        <v>2. รหัสพนักงาน</v>
       </c>
       <c r="B3" t="str">
-        <v>กรอกชื่อเครื่องจักรเป้าหมายในช่อง "2. ย้ายเครื่องทำ OT" -&gt; กำลังพลกะปกติจะอยู่เครื่องเดิม แต่ชั่วโมงและยอดกำลังพล OT จะโอนไปเติมให้เครื่องที่ไปช่วยทำ OT</v>
+        <v>รหัสพนักงาน 5 หลัก เช่น 11848</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>รูปแบบที่ 3: เวลาเข้า-ออกพิเศษตามที่หัวหน้างานสั่ง (Custom Shift Timing)</v>
+        <v>3. เครื่องจักรที่ไปทำ OT (OT Machine)</v>
       </c>
       <c r="B4" t="str">
-        <v>กรอกเวลาในช่อง "3. เวลาเข้าพิเศษ (HH:MM)" เช่น 11:00 -&gt; ระบบจะไม่คิดว่าสาย (isLate = false) และนับชั่วโมงทำงานปกติครบ 8 ชม.</v>
+        <v>ใส่ชื่อเครื่องจักรที่พนักงานไปทำ OT เช่น 320 BANBURY # 2 หรือ Mixer 2 (หากเป็นการย้ายกะปกติก็สามารถใส่เครื่องจักรที่ไปทำได้)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>คำแนะนำการระบุชื่อเครื่องจักร</v>
+        <v>4. เวลา</v>
       </c>
       <c r="B5" t="str">
-        <v>สามารถก๊อปปี้ชื่อเครื่องจักรจากแผ่นงาน "Standard_Machine_List" มาใส่ได้เลย หรือพิมพ์ชื่อย่อ เช่น Mixer 2, Quad, Tuber ระบบจะค้นหาให้อัตโนมัติ</v>
+        <v>กรณีหัวหน้าสั่งให้มาทำงานเวลาพิเศษ เช่น 11:00 หรือ 11:00 - 19:00 (ระบบจะไม่คิดสาย)</v>
       </c>
     </row>
   </sheetData>

--- a/Daily_Adjustments_Template.xlsx
+++ b/Daily_Adjustments_Template.xlsx
@@ -1,11 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <sheets>
-    <sheet name="Daily_Adjustments" sheetId="1" r:id="rId1"/>
-    <sheet name="Standard_Machine_List" sheetId="2" r:id="rId2"/>
-    <sheet name="Instructions_คำแนะนำ" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -399,13 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="38.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:D23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -423,41 +415,41 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>13/09/2026</v>
-      </c>
-      <c r="B2" t="str">
-        <v>11848</v>
+        <v>12/09/2026</v>
+      </c>
+      <c r="B2">
+        <v>3061</v>
       </c>
       <c r="C2" t="str">
-        <v>320 BANBURY # 2</v>
+        <v xml:space="preserve">3-roll </v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>11:00 - 19:00</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>13/09/2026</v>
-      </c>
-      <c r="B3" t="str">
-        <v>03027</v>
+        <v>12/09/2026</v>
+      </c>
+      <c r="B3">
+        <v>10199</v>
       </c>
       <c r="C3" t="str">
-        <v>320 BANBURY # 2</v>
+        <v xml:space="preserve">3-roll </v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>11:00 - 19:00</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>13/09/2026</v>
-      </c>
-      <c r="B4" t="str">
-        <v>12140</v>
+        <v>12/09/2026</v>
+      </c>
+      <c r="B4">
+        <v>12093</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v xml:space="preserve">3-roll </v>
       </c>
       <c r="D4" t="str">
         <v>11:00 - 19:00</v>
@@ -465,323 +457,273 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>12/09/2026</v>
+      </c>
+      <c r="B5">
+        <v>12141</v>
+      </c>
+      <c r="C5" t="str">
+        <v xml:space="preserve">3-roll </v>
+      </c>
+      <c r="D5" t="str">
+        <v>11:00 - 19:00</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>12/09/2026</v>
+      </c>
+      <c r="B6">
+        <v>12187</v>
+      </c>
+      <c r="C6" t="str">
+        <v xml:space="preserve">3-roll </v>
+      </c>
+      <c r="D6" t="str">
+        <v>11:00 - 19:00</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>12/09/2026</v>
+      </c>
+      <c r="B7">
+        <v>12341</v>
+      </c>
+      <c r="C7" t="str">
+        <v xml:space="preserve">3-roll </v>
+      </c>
+      <c r="D7" t="str">
+        <v>11:00 - 19:00</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>12/09/2026</v>
+      </c>
+      <c r="B8">
+        <v>12833</v>
+      </c>
+      <c r="C8" t="str">
+        <v xml:space="preserve">3-roll </v>
+      </c>
+      <c r="D8" t="str">
+        <v>11:00 - 19:00</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
         <v>13/09/2026</v>
       </c>
-      <c r="B5" t="str">
-        <v>12128</v>
-      </c>
-      <c r="C5" t="str">
-        <v>320 BANBURY # 2</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
+      <c r="B9">
+        <v>11848</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Mixer 2</v>
+      </c>
+      <c r="D9" t="str">
+        <v>23.00 - 7.00</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>13/09/2026</v>
+      </c>
+      <c r="B10">
+        <v>12185</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Chaffer Lay-up</v>
+      </c>
+      <c r="D10" t="str">
+        <v>15.00 - 23.00</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>13/09/2026</v>
+      </c>
+      <c r="B11">
+        <v>10705</v>
+      </c>
+      <c r="C11" t="str">
+        <v>54" Band Building</v>
+      </c>
+      <c r="D11" t="str">
+        <v>23.00 - 7.00</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>14/09/2026</v>
+      </c>
+      <c r="B12">
+        <v>12674</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Chaffer Lay-up</v>
+      </c>
+      <c r="D12" t="str">
+        <v>15.00-23.00</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>14/09/2026</v>
+      </c>
+      <c r="B13">
+        <v>12676</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Chaffer Lay-up</v>
+      </c>
+      <c r="D13" t="str">
+        <v>15.00-23.00</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>14/09/2026</v>
+      </c>
+      <c r="B14">
+        <v>12945</v>
+      </c>
+      <c r="C14" t="str">
+        <v>3roll</v>
+      </c>
+      <c r="D14" t="str">
+        <v>15.00-20.00</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15/09/2026</v>
+      </c>
+      <c r="B15">
+        <v>12753</v>
+      </c>
+      <c r="C15" t="str">
+        <v>แทน WAS</v>
+      </c>
+      <c r="D15" t="str">
+        <v>15.00-19.00</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>15/09/2026</v>
+      </c>
+      <c r="B16">
+        <v>12116</v>
+      </c>
+      <c r="C16" t="str">
+        <v>แทน WAS</v>
+      </c>
+      <c r="D16" t="str">
+        <v>15.00-23.00</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>15/09/2026</v>
+      </c>
+      <c r="B17">
+        <v>12185</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Chaffer Lay-up</v>
+      </c>
+      <c r="D17" t="str">
+        <v>15.00-23.00</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>15/09/2026</v>
+      </c>
+      <c r="B18">
+        <v>12462</v>
+      </c>
+      <c r="C18" t="str">
+        <v xml:space="preserve">3roll  </v>
+      </c>
+      <c r="D18" t="str">
+        <v>15.00-18.00</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>15/09/2026</v>
+      </c>
+      <c r="B19">
+        <v>12632</v>
+      </c>
+      <c r="C19" t="str">
+        <v xml:space="preserve">3roll  </v>
+      </c>
+      <c r="D19" t="str">
+        <v>15.00-18.00</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>16/09/2026</v>
+      </c>
+      <c r="B20">
+        <v>12462</v>
+      </c>
+      <c r="C20" t="str">
+        <v xml:space="preserve">3roll  </v>
+      </c>
+      <c r="D20" t="str">
+        <v>15.00-18.00</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>16/09/2026</v>
+      </c>
+      <c r="B21">
+        <v>12945</v>
+      </c>
+      <c r="C21" t="str">
+        <v xml:space="preserve">3roll  </v>
+      </c>
+      <c r="D21" t="str">
+        <v>15.00-18.00</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>16/09/2026</v>
+      </c>
+      <c r="B22">
+        <v>12626</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Chaffer Lay-up</v>
+      </c>
+      <c r="D22" t="str">
+        <v>15.00-23.00</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>16/09/2026</v>
+      </c>
+      <c r="B23">
+        <v>12255</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Trucker 4roll#1</v>
+      </c>
+      <c r="D23" t="str">
+        <v>23.00-07.00</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>รหัส Cost Center</v>
-      </c>
-      <c r="B1" t="str">
-        <v>ชื่อตำแหน่ง / เครื่องจักรในระบบ (Standard Position)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>คำอธิบาย</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>3200</v>
-      </c>
-      <c r="B2" t="str">
-        <v>320 BANBURY # 1</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Mixer 1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>3200</v>
-      </c>
-      <c r="B3" t="str">
-        <v>320 BANBURY # 2</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Mixer 2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3200</v>
-      </c>
-      <c r="B4" t="str">
-        <v>320 Pigment</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Auto Pigment</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>3300</v>
-      </c>
-      <c r="B5" t="str">
-        <v>330 3ROII</v>
-      </c>
-      <c r="C5" t="str">
-        <v>3-Roll Calender</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3700</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Cement (3roll)</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Cement House</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>4110</v>
-      </c>
-      <c r="B7" t="str">
-        <v>411 4Roll#1</v>
-      </c>
-      <c r="C7" t="str">
-        <v>4-Roll Calender 1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>4110</v>
-      </c>
-      <c r="B8" t="str">
-        <v>411 4Roll#2</v>
-      </c>
-      <c r="C8" t="str">
-        <v>4-Roll Calender 2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>4110</v>
-      </c>
-      <c r="B9" t="str">
-        <v>411 Chafer lay up</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Chaffer Lay-up</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>4110</v>
-      </c>
-      <c r="B10" t="str">
-        <v>411 Lux/slitter</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Gum Slitter / Lux</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>4110</v>
-      </c>
-      <c r="B11" t="str">
-        <v>411 Shear Fiscer</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Fischer Cutter</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>4120</v>
-      </c>
-      <c r="B12" t="str">
-        <v>412 Band54"</v>
-      </c>
-      <c r="C12" t="str">
-        <v>54" Band Building</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>4130</v>
-      </c>
-      <c r="B13" t="str">
-        <v>413 Band72"</v>
-      </c>
-      <c r="C13" t="str">
-        <v>72" Band Building</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>4200</v>
-      </c>
-      <c r="B14" t="str">
-        <v>420 Bead Flap</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Bead Flapper</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>4200</v>
-      </c>
-      <c r="B15" t="str">
-        <v>420 Bead insulation</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Bead Insulate</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>4200</v>
-      </c>
-      <c r="B16" t="str">
-        <v>420 Bead Wrap</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Bead Wrapper</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>4200</v>
-      </c>
-      <c r="B17" t="str">
-        <v>420 Hex Bead</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Hex Bead</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>4200</v>
-      </c>
-      <c r="B18" t="str">
-        <v>420 Hot apexer</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Hot Apexer</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>4300</v>
-      </c>
-      <c r="B19" t="str">
-        <v>430 6"x8" Tuber</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Duplex 6" X 8" Extruder</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>4300</v>
-      </c>
-      <c r="B20" t="str">
-        <v>430 Quad</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Quad Extruder</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>3200/4300/4110</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Leader</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Production Team Leader (หัวหน้ากะ)</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
-  <cols>
-    <col min="1" max="1" width="40.83203125" customWidth="1"/>
-    <col min="2" max="2" width="70.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>คอลัมน์ (4 ช่อง)</v>
-      </c>
-      <c r="B1" t="str">
-        <v>คำอธิบาย</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1. วันที่</v>
-      </c>
-      <c r="B2" t="str">
-        <v>วันที่ที่ต้องการปรับเปลี่ยน เช่น 13/09/2026</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2. รหัสพนักงาน</v>
-      </c>
-      <c r="B3" t="str">
-        <v>รหัสพนักงาน 5 หลัก เช่น 11848</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3. เครื่องจักรที่ไปทำ OT (OT Machine)</v>
-      </c>
-      <c r="B4" t="str">
-        <v>ใส่ชื่อเครื่องจักรที่พนักงานไปทำ OT เช่น 320 BANBURY # 2 หรือ Mixer 2 (หากเป็นการย้ายกะปกติก็สามารถใส่เครื่องจักรที่ไปทำได้)</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4. เวลา</v>
-      </c>
-      <c r="B5" t="str">
-        <v>กรณีหัวหน้าสั่งให้มาทำงานเวลาพิเศษ เช่น 11:00 หรือ 11:00 - 19:00 (ระบบจะไม่คิดสาย)</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Daily_Adjustments_Template.xlsx
+++ b/Daily_Adjustments_Template.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -698,7 +698,7 @@
         <v>16/09/2026</v>
       </c>
       <c r="B22">
-        <v>12626</v>
+        <v>12676</v>
       </c>
       <c r="C22" t="str">
         <v>Chaffer Lay-up</v>
@@ -715,15 +715,85 @@
         <v>12255</v>
       </c>
       <c r="C23" t="str">
-        <v>Trucker 4roll#1</v>
+        <v>แทน WAS</v>
       </c>
       <c r="D23" t="str">
         <v>23.00-07.00</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>16/09/2026</v>
+      </c>
+      <c r="B24">
+        <v>12890</v>
+      </c>
+      <c r="C24" t="str">
+        <v xml:space="preserve">Pigment </v>
+      </c>
+      <c r="D24" t="str">
+        <v>23.00-07.00</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>16/09/2026</v>
+      </c>
+      <c r="B25">
+        <v>10705</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Band 54</v>
+      </c>
+      <c r="D25" t="str">
+        <v>23.00-07.00</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>17/09/2026</v>
+      </c>
+      <c r="B26">
+        <v>12809</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Chaffer Lay-up</v>
+      </c>
+      <c r="D26" t="str">
+        <v>07.00-15.00</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>17/09/2026</v>
+      </c>
+      <c r="B27">
+        <v>12732</v>
+      </c>
+      <c r="C27" t="str">
+        <v xml:space="preserve">Pigment </v>
+      </c>
+      <c r="D27" t="str">
+        <v>23.00-07.00</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>17/09/2026</v>
+      </c>
+      <c r="B28">
+        <v>12890</v>
+      </c>
+      <c r="C28" t="str">
+        <v xml:space="preserve">Pigment </v>
+      </c>
+      <c r="D28" t="str">
+        <v>23.00-07.00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D28"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Daily_Adjustments_Template.xlsx
+++ b/Daily_Adjustments_Template.xlsx
@@ -1,41 +1,116 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\10.30 A.M. Production Meeting\สแกนนิ้ว record\ทำงานไม่ตรง ตำแหน่ง\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99119868-2278-4C67-B953-22772FB2602D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="28">
+  <si>
+    <t>วันที่</t>
+  </si>
+  <si>
+    <t>รหัสพนักงาน</t>
+  </si>
+  <si>
+    <t>เครื่องจักรที่ไปทำ OT (OT Machine)</t>
+  </si>
+  <si>
+    <t>เวลา</t>
+  </si>
+  <si>
+    <t>12/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-roll </t>
+  </si>
+  <si>
+    <t>11:00 - 19:00</t>
+  </si>
+  <si>
+    <t>13/09/2026</t>
+  </si>
+  <si>
+    <t>Mixer 2</t>
+  </si>
+  <si>
+    <t>23.00 - 7.00</t>
+  </si>
+  <si>
+    <t>Chaffer Lay-up</t>
+  </si>
+  <si>
+    <t>15.00 - 23.00</t>
+  </si>
+  <si>
+    <t>54" Band Building</t>
+  </si>
+  <si>
+    <t>14/09/2026</t>
+  </si>
+  <si>
+    <t>15.00-23.00</t>
+  </si>
+  <si>
+    <t>3roll</t>
+  </si>
+  <si>
+    <t>15.00-20.00</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>แทน WAS</t>
+  </si>
+  <si>
+    <t>15.00-19.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3roll  </t>
+  </si>
+  <si>
+    <t>15.00-18.00</t>
+  </si>
+  <si>
+    <t>16/09/2026</t>
+  </si>
+  <si>
+    <t>23.00-07.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pigment </t>
+  </si>
+  <si>
+    <t>Band 54</t>
+  </si>
+  <si>
+    <t>17/09/2026</t>
+  </si>
+  <si>
+    <t>07.00-15.00</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +140,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,404 +479,425 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.09765625" customWidth="1"/>
+    <col min="3" max="3" width="14.8984375" customWidth="1"/>
+    <col min="4" max="4" width="15.3984375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>วันที่</v>
-      </c>
-      <c r="B1" t="str">
-        <v>รหัสพนักงาน</v>
-      </c>
-      <c r="C1" t="str">
-        <v>เครื่องจักรที่ไปทำ OT (OT Machine)</v>
-      </c>
-      <c r="D1" t="str">
-        <v>เวลา</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>12/09/2026</v>
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
       </c>
       <c r="B2">
         <v>3061</v>
       </c>
-      <c r="C2" t="str">
-        <v xml:space="preserve">3-roll </v>
-      </c>
-      <c r="D2" t="str">
-        <v>11:00 - 19:00</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>12/09/2026</v>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
         <v>10199</v>
       </c>
-      <c r="C3" t="str">
-        <v xml:space="preserve">3-roll </v>
-      </c>
-      <c r="D3" t="str">
-        <v>11:00 - 19:00</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>12/09/2026</v>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
       </c>
       <c r="B4">
         <v>12093</v>
       </c>
-      <c r="C4" t="str">
-        <v xml:space="preserve">3-roll </v>
-      </c>
-      <c r="D4" t="str">
-        <v>11:00 - 19:00</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>12/09/2026</v>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
       </c>
       <c r="B5">
         <v>12141</v>
       </c>
-      <c r="C5" t="str">
-        <v xml:space="preserve">3-roll </v>
-      </c>
-      <c r="D5" t="str">
-        <v>11:00 - 19:00</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>12/09/2026</v>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
       </c>
       <c r="B6">
         <v>12187</v>
       </c>
-      <c r="C6" t="str">
-        <v xml:space="preserve">3-roll </v>
-      </c>
-      <c r="D6" t="str">
-        <v>11:00 - 19:00</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>12/09/2026</v>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
       </c>
       <c r="B7">
         <v>12341</v>
       </c>
-      <c r="C7" t="str">
-        <v xml:space="preserve">3-roll </v>
-      </c>
-      <c r="D7" t="str">
-        <v>11:00 - 19:00</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>12/09/2026</v>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
       </c>
       <c r="B8">
         <v>12833</v>
       </c>
-      <c r="C8" t="str">
-        <v xml:space="preserve">3-roll </v>
-      </c>
-      <c r="D8" t="str">
-        <v>11:00 - 19:00</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>13/09/2026</v>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>7</v>
       </c>
       <c r="B9">
         <v>11848</v>
       </c>
-      <c r="C9" t="str">
-        <v>Mixer 2</v>
-      </c>
-      <c r="D9" t="str">
-        <v>23.00 - 7.00</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>13/09/2026</v>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
       </c>
       <c r="B10">
         <v>12185</v>
       </c>
-      <c r="C10" t="str">
-        <v>Chaffer Lay-up</v>
-      </c>
-      <c r="D10" t="str">
-        <v>15.00 - 23.00</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>13/09/2026</v>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>7</v>
       </c>
       <c r="B11">
         <v>10705</v>
       </c>
-      <c r="C11" t="str">
-        <v>54" Band Building</v>
-      </c>
-      <c r="D11" t="str">
-        <v>23.00 - 7.00</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>14/09/2026</v>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>13</v>
       </c>
       <c r="B12">
         <v>12674</v>
       </c>
-      <c r="C12" t="str">
-        <v>Chaffer Lay-up</v>
-      </c>
-      <c r="D12" t="str">
-        <v>15.00-23.00</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>14/09/2026</v>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
       </c>
       <c r="B13">
         <v>12676</v>
       </c>
-      <c r="C13" t="str">
-        <v>Chaffer Lay-up</v>
-      </c>
-      <c r="D13" t="str">
-        <v>15.00-23.00</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>14/09/2026</v>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>13</v>
       </c>
       <c r="B14">
         <v>12945</v>
       </c>
-      <c r="C14" t="str">
-        <v>3roll</v>
-      </c>
-      <c r="D14" t="str">
-        <v>15.00-20.00</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>15/09/2026</v>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>17</v>
       </c>
       <c r="B15">
         <v>12753</v>
       </c>
-      <c r="C15" t="str">
-        <v>แทน WAS</v>
-      </c>
-      <c r="D15" t="str">
-        <v>15.00-19.00</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>15/09/2026</v>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>17</v>
       </c>
       <c r="B16">
         <v>12116</v>
       </c>
-      <c r="C16" t="str">
-        <v>แทน WAS</v>
-      </c>
-      <c r="D16" t="str">
-        <v>15.00-23.00</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>15/09/2026</v>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>17</v>
       </c>
       <c r="B17">
         <v>12185</v>
       </c>
-      <c r="C17" t="str">
-        <v>Chaffer Lay-up</v>
-      </c>
-      <c r="D17" t="str">
-        <v>15.00-23.00</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>15/09/2026</v>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>17</v>
       </c>
       <c r="B18">
         <v>12462</v>
       </c>
-      <c r="C18" t="str">
-        <v xml:space="preserve">3roll  </v>
-      </c>
-      <c r="D18" t="str">
-        <v>15.00-18.00</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>15/09/2026</v>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>17</v>
       </c>
       <c r="B19">
         <v>12632</v>
       </c>
-      <c r="C19" t="str">
-        <v xml:space="preserve">3roll  </v>
-      </c>
-      <c r="D19" t="str">
-        <v>15.00-18.00</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>16/09/2026</v>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>22</v>
       </c>
       <c r="B20">
         <v>12462</v>
       </c>
-      <c r="C20" t="str">
-        <v xml:space="preserve">3roll  </v>
-      </c>
-      <c r="D20" t="str">
-        <v>15.00-18.00</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>16/09/2026</v>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>22</v>
       </c>
       <c r="B21">
         <v>12945</v>
       </c>
-      <c r="C21" t="str">
-        <v xml:space="preserve">3roll  </v>
-      </c>
-      <c r="D21" t="str">
-        <v>15.00-18.00</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>16/09/2026</v>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>22</v>
       </c>
       <c r="B22">
         <v>12676</v>
       </c>
-      <c r="C22" t="str">
-        <v>Chaffer Lay-up</v>
-      </c>
-      <c r="D22" t="str">
-        <v>15.00-23.00</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>16/09/2026</v>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>22</v>
       </c>
       <c r="B23">
         <v>12255</v>
       </c>
-      <c r="C23" t="str">
-        <v>แทน WAS</v>
-      </c>
-      <c r="D23" t="str">
-        <v>23.00-07.00</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>16/09/2026</v>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>22</v>
       </c>
       <c r="B24">
         <v>12890</v>
       </c>
-      <c r="C24" t="str">
-        <v xml:space="preserve">Pigment </v>
-      </c>
-      <c r="D24" t="str">
-        <v>23.00-07.00</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>16/09/2026</v>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>22</v>
       </c>
       <c r="B25">
         <v>10705</v>
       </c>
-      <c r="C25" t="str">
-        <v>Band 54</v>
-      </c>
-      <c r="D25" t="str">
-        <v>23.00-07.00</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>17/09/2026</v>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>26</v>
       </c>
       <c r="B26">
         <v>12809</v>
       </c>
-      <c r="C26" t="str">
-        <v>Chaffer Lay-up</v>
-      </c>
-      <c r="D26" t="str">
-        <v>07.00-15.00</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>17/09/2026</v>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>26</v>
       </c>
       <c r="B27">
         <v>12732</v>
       </c>
-      <c r="C27" t="str">
-        <v xml:space="preserve">Pigment </v>
-      </c>
-      <c r="D27" t="str">
-        <v>23.00-07.00</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>17/09/2026</v>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>26</v>
       </c>
       <c r="B28">
         <v>12890</v>
       </c>
-      <c r="C28" t="str">
-        <v xml:space="preserve">Pigment </v>
-      </c>
-      <c r="D28" t="str">
-        <v>23.00-07.00</v>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>12809</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D28"/>
+    <ignoredError sqref="A1:D28" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Daily_Adjustments_Template.xlsx
+++ b/Daily_Adjustments_Template.xlsx
@@ -1,116 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\10.30 A.M. Production Meeting\สแกนนิ้ว record\ทำงานไม่ตรง ตำแหน่ง\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99119868-2278-4C67-B953-22772FB2602D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="28">
-  <si>
-    <t>วันที่</t>
-  </si>
-  <si>
-    <t>รหัสพนักงาน</t>
-  </si>
-  <si>
-    <t>เครื่องจักรที่ไปทำ OT (OT Machine)</t>
-  </si>
-  <si>
-    <t>เวลา</t>
-  </si>
-  <si>
-    <t>12/09/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-roll </t>
-  </si>
-  <si>
-    <t>11:00 - 19:00</t>
-  </si>
-  <si>
-    <t>13/09/2026</t>
-  </si>
-  <si>
-    <t>Mixer 2</t>
-  </si>
-  <si>
-    <t>23.00 - 7.00</t>
-  </si>
-  <si>
-    <t>Chaffer Lay-up</t>
-  </si>
-  <si>
-    <t>15.00 - 23.00</t>
-  </si>
-  <si>
-    <t>54" Band Building</t>
-  </si>
-  <si>
-    <t>14/09/2026</t>
-  </si>
-  <si>
-    <t>15.00-23.00</t>
-  </si>
-  <si>
-    <t>3roll</t>
-  </si>
-  <si>
-    <t>15.00-20.00</t>
-  </si>
-  <si>
-    <t>15/09/2026</t>
-  </si>
-  <si>
-    <t>แทน WAS</t>
-  </si>
-  <si>
-    <t>15.00-19.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3roll  </t>
-  </si>
-  <si>
-    <t>15.00-18.00</t>
-  </si>
-  <si>
-    <t>16/09/2026</t>
-  </si>
-  <si>
-    <t>23.00-07.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pigment </t>
-  </si>
-  <si>
-    <t>Band 54</t>
-  </si>
-  <si>
-    <t>17/09/2026</t>
-  </si>
-  <si>
-    <t>07.00-15.00</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -140,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -479,425 +396,460 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.09765625" customWidth="1"/>
-    <col min="3" max="3" width="14.8984375" customWidth="1"/>
-    <col min="4" max="4" width="15.3984375" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D32"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>วันที่</v>
+      </c>
+      <c r="B1" t="str">
+        <v>รหัสพนักงาน</v>
+      </c>
+      <c r="C1" t="str">
+        <v>เครื่องจักรที่ไปทำ OT (OT Machine)</v>
+      </c>
+      <c r="D1" t="str">
+        <v>เวลา</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>12/09/2026</v>
       </c>
       <c r="B2">
         <v>3061</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
+      <c r="C2" t="str">
+        <v xml:space="preserve">3-roll </v>
+      </c>
+      <c r="D2" t="str">
+        <v>11:00 - 19:00</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>12/09/2026</v>
       </c>
       <c r="B3">
         <v>10199</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
+      <c r="C3" t="str">
+        <v xml:space="preserve">3-roll </v>
+      </c>
+      <c r="D3" t="str">
+        <v>11:00 - 19:00</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>12/09/2026</v>
       </c>
       <c r="B4">
         <v>12093</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
+      <c r="C4" t="str">
+        <v xml:space="preserve">3-roll </v>
+      </c>
+      <c r="D4" t="str">
+        <v>11:00 - 19:00</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>12/09/2026</v>
       </c>
       <c r="B5">
         <v>12141</v>
       </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
+      <c r="C5" t="str">
+        <v xml:space="preserve">3-roll </v>
+      </c>
+      <c r="D5" t="str">
+        <v>11:00 - 19:00</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>12/09/2026</v>
       </c>
       <c r="B6">
         <v>12187</v>
       </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>4</v>
+      <c r="C6" t="str">
+        <v xml:space="preserve">3-roll </v>
+      </c>
+      <c r="D6" t="str">
+        <v>11:00 - 19:00</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>12/09/2026</v>
       </c>
       <c r="B7">
         <v>12341</v>
       </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>4</v>
+      <c r="C7" t="str">
+        <v xml:space="preserve">3-roll </v>
+      </c>
+      <c r="D7" t="str">
+        <v>11:00 - 19:00</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>12/09/2026</v>
       </c>
       <c r="B8">
         <v>12833</v>
       </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
+      <c r="C8" t="str">
+        <v xml:space="preserve">3-roll </v>
+      </c>
+      <c r="D8" t="str">
+        <v>11:00 - 19:00</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>13/09/2026</v>
       </c>
       <c r="B9">
         <v>11848</v>
       </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>7</v>
+      <c r="C9" t="str">
+        <v>Mixer 2</v>
+      </c>
+      <c r="D9" t="str">
+        <v>23.00 - 7.00</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>13/09/2026</v>
       </c>
       <c r="B10">
         <v>12185</v>
       </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>7</v>
+      <c r="C10" t="str">
+        <v>Chaffer Lay-up</v>
+      </c>
+      <c r="D10" t="str">
+        <v>15.00 - 23.00</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>13/09/2026</v>
       </c>
       <c r="B11">
         <v>10705</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>13</v>
+      <c r="C11" t="str">
+        <v>54" Band Building</v>
+      </c>
+      <c r="D11" t="str">
+        <v>23.00 - 7.00</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>14/09/2026</v>
       </c>
       <c r="B12">
         <v>12674</v>
       </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>13</v>
+      <c r="C12" t="str">
+        <v>Chaffer Lay-up</v>
+      </c>
+      <c r="D12" t="str">
+        <v>15.00-23.00</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>14/09/2026</v>
       </c>
       <c r="B13">
         <v>12676</v>
       </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>13</v>
+      <c r="C13" t="str">
+        <v>Chaffer Lay-up</v>
+      </c>
+      <c r="D13" t="str">
+        <v>15.00-23.00</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>14/09/2026</v>
       </c>
       <c r="B14">
         <v>12945</v>
       </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>17</v>
+      <c r="C14" t="str">
+        <v>3roll</v>
+      </c>
+      <c r="D14" t="str">
+        <v>15.00-20.00</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>15/09/2026</v>
       </c>
       <c r="B15">
         <v>12753</v>
       </c>
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>17</v>
+      <c r="C15" t="str">
+        <v>แทน WAS</v>
+      </c>
+      <c r="D15" t="str">
+        <v>15.00-19.00</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>15/09/2026</v>
       </c>
       <c r="B16">
         <v>12116</v>
       </c>
-      <c r="C16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>17</v>
+      <c r="C16" t="str">
+        <v>แทน WAS</v>
+      </c>
+      <c r="D16" t="str">
+        <v>15.00-23.00</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>15/09/2026</v>
       </c>
       <c r="B17">
         <v>12185</v>
       </c>
-      <c r="C17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>17</v>
+      <c r="C17" t="str">
+        <v>Chaffer Lay-up</v>
+      </c>
+      <c r="D17" t="str">
+        <v>15.00-23.00</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>15/09/2026</v>
       </c>
       <c r="B18">
         <v>12462</v>
       </c>
-      <c r="C18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>17</v>
+      <c r="C18" t="str">
+        <v xml:space="preserve">3roll  </v>
+      </c>
+      <c r="D18" t="str">
+        <v>15.00-18.00</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>15/09/2026</v>
       </c>
       <c r="B19">
         <v>12632</v>
       </c>
-      <c r="C19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>22</v>
+      <c r="C19" t="str">
+        <v xml:space="preserve">3roll  </v>
+      </c>
+      <c r="D19" t="str">
+        <v>15.00-18.00</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>16/09/2026</v>
       </c>
       <c r="B20">
         <v>12462</v>
       </c>
-      <c r="C20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>22</v>
+      <c r="C20" t="str">
+        <v xml:space="preserve">3roll  </v>
+      </c>
+      <c r="D20" t="str">
+        <v>15.00-18.00</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>16/09/2026</v>
       </c>
       <c r="B21">
         <v>12945</v>
       </c>
-      <c r="C21" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>22</v>
+      <c r="C21" t="str">
+        <v xml:space="preserve">3roll  </v>
+      </c>
+      <c r="D21" t="str">
+        <v>15.00-18.00</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>16/09/2026</v>
       </c>
       <c r="B22">
         <v>12676</v>
       </c>
-      <c r="C22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>22</v>
+      <c r="C22" t="str">
+        <v>Chaffer Lay-up</v>
+      </c>
+      <c r="D22" t="str">
+        <v>15.00-23.00</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>16/09/2026</v>
       </c>
       <c r="B23">
         <v>12255</v>
       </c>
-      <c r="C23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>22</v>
+      <c r="C23" t="str">
+        <v>แทน WAS</v>
+      </c>
+      <c r="D23" t="str">
+        <v>23.00-07.00</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>16/09/2026</v>
       </c>
       <c r="B24">
         <v>12890</v>
       </c>
-      <c r="C24" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>22</v>
+      <c r="C24" t="str">
+        <v xml:space="preserve">Pigment </v>
+      </c>
+      <c r="D24" t="str">
+        <v>23.00-07.00</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>16/09/2026</v>
       </c>
       <c r="B25">
         <v>10705</v>
       </c>
-      <c r="C25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>26</v>
+      <c r="C25" t="str">
+        <v>Band 54</v>
+      </c>
+      <c r="D25" t="str">
+        <v>23.00-07.00</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>17/09/2026</v>
       </c>
       <c r="B26">
         <v>12809</v>
       </c>
-      <c r="C26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>26</v>
+      <c r="C26" t="str">
+        <v>Chaffer Lay-up</v>
+      </c>
+      <c r="D26" t="str">
+        <v>07.00-15.00</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>17/09/2026</v>
       </c>
       <c r="B27">
         <v>12732</v>
       </c>
-      <c r="C27" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>26</v>
+      <c r="C27" t="str">
+        <v xml:space="preserve">Pigment </v>
+      </c>
+      <c r="D27" t="str">
+        <v>23.00-07.00</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>17/09/2026</v>
       </c>
       <c r="B28">
         <v>12890</v>
       </c>
-      <c r="C28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>26</v>
+      <c r="C28" t="str">
+        <v xml:space="preserve">Pigment </v>
+      </c>
+      <c r="D28" t="str">
+        <v>23.00-07.00</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>17/09/2026</v>
       </c>
       <c r="B29">
         <v>12809</v>
       </c>
-      <c r="C29" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" t="s">
-        <v>23</v>
+      <c r="C29" t="str">
+        <v>Chaffer Lay-up</v>
+      </c>
+      <c r="D29" t="str">
+        <v>15.00-23.00</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>17/09/2026</v>
+      </c>
+      <c r="B30">
+        <v>12186</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Band54''</v>
+      </c>
+      <c r="D30" t="str">
+        <v>15.00-23.00</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>17/09/2026</v>
+      </c>
+      <c r="B31">
+        <v>9833</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Band54''</v>
+      </c>
+      <c r="D31" t="str">
+        <v>23.00-07.00</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>17/09/2026</v>
+      </c>
+      <c r="B32">
+        <v>12185</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Band54''</v>
+      </c>
+      <c r="D32" t="str">
+        <v>23.00-07.00</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:D28" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D32"/>
   </ignoredErrors>
 </worksheet>
 </file>